--- a/data+Timegraphs.xlsx
+++ b/data+Timegraphs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inesappelquist/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4F5F6D-14B1-5045-9C18-89DCDDF48A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB38BC62-9C7A-F749-8483-2BC778D753F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,20 +28,6 @@
     <sheet name="P6d" sheetId="13" r:id="rId13"/>
     <sheet name="Graphs" sheetId="14" r:id="rId14"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Graphs!$A$46:$A$50</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Graphs!$B$46:$B$50</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Graphs!$C$34</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Graphs!$C$35:$C$39</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Graphs!$C$45</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Graphs!$C$46:$C$50</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Graphs!$A$35:$A$39</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Graphs!$B$35:$B$39</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Graphs!$C$34</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Graphs!$C$35:$C$39</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Graphs!$A$35:$A$39</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Graphs!$B$35:$B$39</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -11292,7 +11278,7 @@
               <a:p>
                 <a:r>
                   <a:rPr lang="en-GB"/>
-                  <a:t>Accuracy (%)</a:t>
+                  <a:t>'Accuracy (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -11362,7 +11348,7 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="7.327484064491939E-2"/>
-          <c:y val="0.1545549988069673"/>
+          <c:y val="0.13846063382088006"/>
           <c:w val="0.86124896887889013"/>
           <c:h val="0.66088672154617034"/>
         </c:manualLayout>
@@ -11485,6 +11471,13 @@
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
@@ -11492,6 +11485,12 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -11541,6 +11540,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="ED7D31"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-5E4E-3D4A-B50D-D8CD66F4DE9A}"/>
             </c:ext>
@@ -11556,7 +11570,6 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="48650112"/>
         <c:axId val="48672768"/>
       </c:barChart>
@@ -11585,14 +11598,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Graphs!$A$35:$A$39</c:f>
@@ -11809,6 +11814,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="435016064"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -11873,7 +11879,7 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="7.327484064491939E-2"/>
-          <c:y val="0.1545549988069673"/>
+          <c:y val="0.13548722732670948"/>
           <c:w val="0.86124896887889013"/>
           <c:h val="0.66088672154617034"/>
         </c:manualLayout>
@@ -11996,6 +12002,13 @@
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
@@ -12003,6 +12016,12 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -12043,7 +12062,7 @@
                   <c:v>47.55</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>36.45</c:v>
+                  <c:v>36.450000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>22.9</c:v>
@@ -12052,6 +12071,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="ED7D31"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-5E4E-3D4A-B50D-D8CD66F4DE9A}"/>
             </c:ext>
@@ -12067,7 +12101,6 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="48650112"/>
         <c:axId val="48672768"/>
       </c:barChart>
@@ -12096,14 +12129,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Graphs!$A$46:$A$50</c:f>
@@ -12320,6 +12345,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="416194880"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -17515,14 +17541,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>186265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>84667</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17549,16 +17575,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>169333</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>67734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>999066</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17585,16 +17611,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>186267</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>135467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>135466</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17621,16 +17647,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>186267</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>135466</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>135467</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
